--- a/MU/Test upload format/Normal/2029 - 2030/UPdate_Mudra_borrowers3.xlsx
+++ b/MU/Test upload format/Normal/2029 - 2030/UPdate_Mudra_borrowers3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="38">
   <si>
     <t>custid</t>
   </si>
@@ -89,46 +89,58 @@
     <t>HomeStay</t>
   </si>
   <si>
-    <t>SDR2425001</t>
+    <t>Q2CRCGFEE01</t>
+  </si>
+  <si>
+    <t>1000</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>01-04-2021</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>SDR2425002</t>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>01-12-2026</t>
+  </si>
+  <si>
+    <t>900000</t>
+  </si>
+  <si>
+    <t>01-07-2026</t>
   </si>
   <si>
     <t>S</t>
   </si>
   <si>
-    <t>SDR2425003</t>
+    <t>Q2CRCGFEE08</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>100000</t>
   </si>
   <si>
     <t>K</t>
   </si>
   <si>
-    <t>SDR2425004</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>SDR2425005</t>
-  </si>
-  <si>
-    <t>TP</t>
+    <t>Q2CRCGFEE14</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>800000</t>
+  </si>
+  <si>
+    <t>01-08-2026</t>
+  </si>
+  <si>
+    <t>Q2CRCGFEE19</t>
+  </si>
+  <si>
+    <t>10-08-2026</t>
   </si>
 </sst>
 </file>
@@ -141,7 +153,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,12 +168,6 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -308,7 +314,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -317,6 +323,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -502,7 +514,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -535,21 +547,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -669,137 +666,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -818,11 +815,12 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1175,11 +1173,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T6"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="5"/>
+  <dimension ref="A1:T5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="20.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="17.2857142857143" customWidth="1"/>
     <col min="6" max="6" width="15.7142857142857" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="9" max="9" width="13.1428571428571" customWidth="1"/>
@@ -1261,177 +1260,152 @@
       <c r="B2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="8">
-        <v>1000</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="8" t="s">
         <v>21</v>
       </c>
+      <c r="D2" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="E2" s="10"/>
-      <c r="F2" s="8">
-        <v>9000</v>
-      </c>
-      <c r="G2" s="10" t="s">
+      <c r="F2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
       <c r="I2" s="10"/>
-      <c r="J2"/>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
-      <c r="M2" s="8">
-        <v>10000</v>
-      </c>
-      <c r="N2" s="10" t="s">
+      <c r="M2" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" t="s">
         <v>22</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="T2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="8">
-        <v>100</v>
-      </c>
-      <c r="D3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="8">
-        <v>44500</v>
-      </c>
-      <c r="G3" s="10" t="s">
+      <c r="D3" s="13" t="s">
         <v>22</v>
       </c>
+      <c r="F3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="10"/>
-      <c r="J3"/>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
-      <c r="M3" s="8">
-        <v>50000</v>
-      </c>
-      <c r="N3" s="10" t="s">
+      <c r="M3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="T3" t="s">
         <v>22</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S3" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="T3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="8">
-        <v>200000</v>
-      </c>
-      <c r="D4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="8">
-        <v>300000</v>
-      </c>
-      <c r="G4" s="10" t="s">
+      <c r="D4" s="13" t="s">
         <v>22</v>
       </c>
+      <c r="F4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4"/>
+        <v>22</v>
+      </c>
       <c r="K4">
         <v>1</v>
       </c>
       <c r="L4">
         <v>1</v>
       </c>
-      <c r="M4" s="8">
-        <v>500000</v>
-      </c>
-      <c r="N4" s="10" t="s">
+      <c r="M4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" t="s">
         <v>22</v>
-      </c>
-      <c r="P4" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="T4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="8">
-        <v>100000</v>
-      </c>
-      <c r="D5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="8">
-        <v>400000</v>
-      </c>
-      <c r="G5" s="10" t="s">
+      <c r="D5" s="13" t="s">
         <v>22</v>
       </c>
+      <c r="F5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1439,76 +1413,17 @@
       <c r="L5">
         <v>1</v>
       </c>
-      <c r="M5" s="8">
-        <v>600000</v>
-      </c>
-      <c r="N5" s="10" t="s">
+      <c r="M5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="T5" t="s">
         <v>22</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S5" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="T5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
-      <c r="A6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="8">
-        <v>300000</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="8">
-        <v>550000</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6" s="8">
-        <v>800000</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="P6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="R6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S6" t="s">
-        <v>33</v>
-      </c>
-      <c r="T6" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
